--- a/amkr/dist/20261025_艾克爾模型_v0.2.xlsx
+++ b/amkr/dist/20261025_艾克爾模型_v0.2.xlsx
@@ -3648,7 +3648,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4184,7 +4184,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4402,7 +4402,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4523,7 +4523,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4644,7 +4644,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4765,7 +4765,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4886,7 +4886,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5045,7 +5045,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5102,7 +5102,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5659,7 +5659,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5810,7 +5810,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36785,7 +36785,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
